--- a/artfynd/A 36470-2024 artfynd.xlsx
+++ b/artfynd/A 36470-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108141</v>
+        <v>120107799</v>
       </c>
       <c r="B2" t="n">
         <v>57310</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584574</v>
+        <v>584425</v>
       </c>
       <c r="R2" t="n">
-        <v>7057137</v>
+        <v>7056965</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108467</v>
+        <v>120107427</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +808,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584625</v>
+        <v>584332</v>
       </c>
       <c r="R3" t="n">
-        <v>7057173</v>
+        <v>7056924</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108009</v>
+        <v>120107871</v>
       </c>
       <c r="B4" t="n">
-        <v>82305</v>
+        <v>90558</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584477</v>
+        <v>584459</v>
       </c>
       <c r="R4" t="n">
-        <v>7056963</v>
+        <v>7056926</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120107427</v>
+        <v>120108290</v>
       </c>
       <c r="B5" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,42 +1037,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584332</v>
+        <v>584580</v>
       </c>
       <c r="R5" t="n">
-        <v>7056924</v>
+        <v>7057147</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120107381</v>
+        <v>120108359</v>
       </c>
       <c r="B6" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,16 +1154,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1172,21 +1172,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584368</v>
+        <v>584598</v>
       </c>
       <c r="R6" t="n">
-        <v>7056918</v>
+        <v>7057170</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120108359</v>
+        <v>120108467</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584598</v>
+        <v>584625</v>
       </c>
       <c r="R7" t="n">
-        <v>7057170</v>
+        <v>7057173</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120108230</v>
+        <v>120107381</v>
       </c>
       <c r="B8" t="n">
-        <v>82305</v>
+        <v>57326</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,34 +1388,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584514</v>
+        <v>584368</v>
       </c>
       <c r="R8" t="n">
-        <v>7057145</v>
+        <v>7056918</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120108535</v>
+        <v>120108343</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,24 +1505,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
@@ -1530,7 +1540,7 @@
         <v>7057141</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1559,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,12 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120107799</v>
+        <v>120108230</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>82305</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,21 +1622,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1641,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584425</v>
+        <v>584514</v>
       </c>
       <c r="R10" t="n">
-        <v>7056965</v>
+        <v>7057145</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,12 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,12 +1706,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120108290</v>
+        <v>120108141</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584580</v>
+        <v>584574</v>
       </c>
       <c r="R12" t="n">
-        <v>7057147</v>
+        <v>7057137</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,12 +1935,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120108343</v>
+        <v>120108009</v>
       </c>
       <c r="B15" t="n">
-        <v>57463</v>
+        <v>82305</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,42 +2197,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584643</v>
+        <v>584477</v>
       </c>
       <c r="R15" t="n">
-        <v>7057141</v>
+        <v>7056963</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2261,7 +2256,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2271,7 +2266,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,22 +2281,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120107871</v>
+        <v>120108535</v>
       </c>
       <c r="B16" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2314,21 +2309,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2338,10 +2333,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584459</v>
+        <v>584643</v>
       </c>
       <c r="R16" t="n">
-        <v>7056926</v>
+        <v>7057141</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2373,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,7 +2378,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,12 +2398,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 36470-2024 artfynd.xlsx
+++ b/artfynd/A 36470-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120107799</v>
+        <v>120108230</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>82305</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584425</v>
+        <v>584514</v>
       </c>
       <c r="R2" t="n">
-        <v>7056965</v>
+        <v>7057145</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120107427</v>
+        <v>120108290</v>
       </c>
       <c r="B3" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,42 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584332</v>
+        <v>584580</v>
       </c>
       <c r="R3" t="n">
-        <v>7056924</v>
+        <v>7057147</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120107871</v>
+        <v>120107427</v>
       </c>
       <c r="B4" t="n">
-        <v>90558</v>
+        <v>57463</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,37 +920,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584459</v>
+        <v>584332</v>
       </c>
       <c r="R4" t="n">
-        <v>7056926</v>
+        <v>7056924</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,19 +1009,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108290</v>
+        <v>120108359</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584580</v>
+        <v>584598</v>
       </c>
       <c r="R5" t="n">
-        <v>7057147</v>
+        <v>7057170</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120108359</v>
+        <v>120107871</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584598</v>
+        <v>584459</v>
       </c>
       <c r="R6" t="n">
-        <v>7057170</v>
+        <v>7056926</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120108467</v>
+        <v>120107534</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1295,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584625</v>
+        <v>584364</v>
       </c>
       <c r="R7" t="n">
-        <v>7057173</v>
+        <v>7056956</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,12 +1335,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,22 +1355,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120107381</v>
+        <v>120108141</v>
       </c>
       <c r="B8" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,16 +1383,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1406,21 +1401,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584368</v>
+        <v>584574</v>
       </c>
       <c r="R8" t="n">
-        <v>7056918</v>
+        <v>7057137</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1452,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,22 +1472,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120108343</v>
+        <v>120107400</v>
       </c>
       <c r="B9" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,42 +1500,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584643</v>
+        <v>584327</v>
       </c>
       <c r="R9" t="n">
-        <v>7057141</v>
+        <v>7056918</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1569,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1569,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120108230</v>
+        <v>120108343</v>
       </c>
       <c r="B10" t="n">
-        <v>82305</v>
+        <v>57463</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,37 +1617,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584514</v>
+        <v>584643</v>
       </c>
       <c r="R10" t="n">
-        <v>7057145</v>
+        <v>7057141</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,22 +1706,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120108385</v>
+        <v>120108467</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,21 +1734,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1758,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584601</v>
+        <v>584625</v>
       </c>
       <c r="R11" t="n">
-        <v>7057163</v>
+        <v>7057173</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1803,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120108141</v>
+        <v>120107381</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,16 +1851,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1864,16 +1869,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584574</v>
+        <v>584368</v>
       </c>
       <c r="R12" t="n">
-        <v>7057137</v>
+        <v>7056918</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,12 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,19 +1940,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120107534</v>
+        <v>120107799</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -1987,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584364</v>
+        <v>584425</v>
       </c>
       <c r="R13" t="n">
-        <v>7056956</v>
+        <v>7056965</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2064,7 +2069,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120107400</v>
+        <v>120108535</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -2104,10 +2109,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584327</v>
+        <v>584643</v>
       </c>
       <c r="R14" t="n">
-        <v>7056918</v>
+        <v>7057141</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2144,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,12 +2154,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2181,10 +2186,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120108009</v>
+        <v>120108385</v>
       </c>
       <c r="B15" t="n">
-        <v>82305</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,21 +2202,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2221,10 +2226,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584477</v>
+        <v>584601</v>
       </c>
       <c r="R15" t="n">
-        <v>7056963</v>
+        <v>7057163</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,7 +2261,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2266,7 +2271,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2293,10 +2298,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120108535</v>
+        <v>120108009</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>82305</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2309,21 +2314,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2333,10 +2338,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584643</v>
+        <v>584477</v>
       </c>
       <c r="R16" t="n">
-        <v>7057141</v>
+        <v>7056963</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2368,7 +2373,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2378,12 +2383,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,12 +2398,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 36470-2024 artfynd.xlsx
+++ b/artfynd/A 36470-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108230</v>
+        <v>120107400</v>
       </c>
       <c r="B2" t="n">
-        <v>82305</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584514</v>
+        <v>584327</v>
       </c>
       <c r="R2" t="n">
-        <v>7057145</v>
+        <v>7056918</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108290</v>
+        <v>120108009</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>82305</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584580</v>
+        <v>584477</v>
       </c>
       <c r="R3" t="n">
-        <v>7057147</v>
+        <v>7056963</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120107427</v>
+        <v>120108535</v>
       </c>
       <c r="B4" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,42 +920,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584332</v>
+        <v>584643</v>
       </c>
       <c r="R4" t="n">
-        <v>7056924</v>
+        <v>7057141</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108359</v>
+        <v>120107427</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,37 +1037,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584598</v>
+        <v>584332</v>
       </c>
       <c r="R5" t="n">
-        <v>7057170</v>
+        <v>7056924</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120107871</v>
+        <v>120108343</v>
       </c>
       <c r="B6" t="n">
-        <v>90558</v>
+        <v>57463</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,37 +1154,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584459</v>
+        <v>584643</v>
       </c>
       <c r="R6" t="n">
-        <v>7056926</v>
+        <v>7057141</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,19 +1243,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120107534</v>
+        <v>120108359</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1290,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584364</v>
+        <v>584598</v>
       </c>
       <c r="R7" t="n">
-        <v>7056956</v>
+        <v>7057170</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,12 +1340,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,22 +1360,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120108141</v>
+        <v>120107871</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584574</v>
+        <v>584459</v>
       </c>
       <c r="R8" t="n">
-        <v>7057137</v>
+        <v>7056926</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,12 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,22 +1472,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120107400</v>
+        <v>120107381</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,16 +1500,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1518,13 +1518,18 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584327</v>
+        <v>584368</v>
       </c>
       <c r="R9" t="n">
         <v>7056918</v>
@@ -1559,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,12 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,22 +1589,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120108343</v>
+        <v>120108230</v>
       </c>
       <c r="B10" t="n">
-        <v>57463</v>
+        <v>82305</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,42 +1617,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584643</v>
+        <v>584514</v>
       </c>
       <c r="R10" t="n">
-        <v>7057141</v>
+        <v>7057145</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1681,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,22 +1701,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120108467</v>
+        <v>120108385</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,21 +1729,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1758,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584625</v>
+        <v>584601</v>
       </c>
       <c r="R11" t="n">
-        <v>7057173</v>
+        <v>7057163</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,12 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120107381</v>
+        <v>120108141</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,16 +1841,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1869,21 +1859,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584368</v>
+        <v>584574</v>
       </c>
       <c r="R12" t="n">
-        <v>7056918</v>
+        <v>7057137</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1910,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,12 +1930,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2069,7 +2059,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120108535</v>
+        <v>120108467</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -2109,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584643</v>
+        <v>584625</v>
       </c>
       <c r="R14" t="n">
-        <v>7057141</v>
+        <v>7057173</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2144,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2154,12 +2144,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,22 +2164,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120108385</v>
+        <v>120107534</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2202,21 +2192,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2226,10 +2216,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584601</v>
+        <v>584364</v>
       </c>
       <c r="R15" t="n">
-        <v>7057163</v>
+        <v>7056956</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2261,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2271,7 +2261,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,22 +2281,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120108009</v>
+        <v>120108290</v>
       </c>
       <c r="B16" t="n">
-        <v>82305</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2314,21 +2309,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2338,10 +2333,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584477</v>
+        <v>584580</v>
       </c>
       <c r="R16" t="n">
-        <v>7056963</v>
+        <v>7057147</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2373,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,7 +2378,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 36470-2024 artfynd.xlsx
+++ b/artfynd/A 36470-2024 artfynd.xlsx
@@ -2059,7 +2059,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120108467</v>
+        <v>120107534</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584625</v>
+        <v>584364</v>
       </c>
       <c r="R14" t="n">
-        <v>7057173</v>
+        <v>7056956</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,19 +2164,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120107534</v>
+        <v>120108290</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584364</v>
+        <v>584580</v>
       </c>
       <c r="R15" t="n">
-        <v>7056956</v>
+        <v>7057147</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,19 +2281,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120108290</v>
+        <v>120108467</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584580</v>
+        <v>584625</v>
       </c>
       <c r="R16" t="n">
-        <v>7057147</v>
+        <v>7057173</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">

--- a/artfynd/A 36470-2024 artfynd.xlsx
+++ b/artfynd/A 36470-2024 artfynd.xlsx
@@ -2059,7 +2059,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120107534</v>
+        <v>120108467</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584364</v>
+        <v>584625</v>
       </c>
       <c r="R14" t="n">
-        <v>7056956</v>
+        <v>7057173</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,19 +2164,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120108290</v>
+        <v>120107534</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584580</v>
+        <v>584364</v>
       </c>
       <c r="R15" t="n">
-        <v>7057147</v>
+        <v>7056956</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,19 +2281,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120108467</v>
+        <v>120108290</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584625</v>
+        <v>584580</v>
       </c>
       <c r="R16" t="n">
-        <v>7057173</v>
+        <v>7057147</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">

--- a/artfynd/A 36470-2024 artfynd.xlsx
+++ b/artfynd/A 36470-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120107400</v>
+        <v>120107871</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584327</v>
+        <v>584459</v>
       </c>
       <c r="R2" t="n">
-        <v>7056918</v>
+        <v>7056926</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108009</v>
+        <v>120107799</v>
       </c>
       <c r="B3" t="n">
-        <v>82305</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584477</v>
+        <v>584425</v>
       </c>
       <c r="R3" t="n">
-        <v>7056963</v>
+        <v>7056965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108535</v>
+        <v>120107400</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584643</v>
+        <v>584327</v>
       </c>
       <c r="R4" t="n">
-        <v>7057141</v>
+        <v>7056918</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120107427</v>
+        <v>120108230</v>
       </c>
       <c r="B5" t="n">
-        <v>57463</v>
+        <v>82321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,42 +1037,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584332</v>
+        <v>584514</v>
       </c>
       <c r="R5" t="n">
-        <v>7056924</v>
+        <v>7057145</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120108343</v>
+        <v>120108359</v>
       </c>
       <c r="B6" t="n">
-        <v>57463</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,42 +1149,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584643</v>
+        <v>584598</v>
       </c>
       <c r="R6" t="n">
-        <v>7057141</v>
+        <v>7057170</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1218,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,22 +1238,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120108359</v>
+        <v>120108467</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584598</v>
+        <v>584625</v>
       </c>
       <c r="R7" t="n">
-        <v>7057170</v>
+        <v>7057173</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1372,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120107871</v>
+        <v>120108535</v>
       </c>
       <c r="B8" t="n">
-        <v>90558</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584459</v>
+        <v>584643</v>
       </c>
       <c r="R8" t="n">
-        <v>7056926</v>
+        <v>7057141</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1452,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,22 +1472,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120107381</v>
+        <v>120108343</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
+        <v>57473</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,21 +1500,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584368</v>
+        <v>584643</v>
       </c>
       <c r="R9" t="n">
-        <v>7056918</v>
+        <v>7057141</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,22 +1589,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120108230</v>
+        <v>120108385</v>
       </c>
       <c r="B10" t="n">
-        <v>82305</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,21 +1617,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584514</v>
+        <v>584601</v>
       </c>
       <c r="R10" t="n">
-        <v>7057145</v>
+        <v>7057163</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120108385</v>
+        <v>120108009</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>82321</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,21 +1729,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584601</v>
+        <v>584477</v>
       </c>
       <c r="R11" t="n">
-        <v>7057163</v>
+        <v>7056963</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120108141</v>
+        <v>120107427</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,37 +1841,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584574</v>
+        <v>584332</v>
       </c>
       <c r="R12" t="n">
-        <v>7057137</v>
+        <v>7056924</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,12 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120107799</v>
+        <v>120108290</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584425</v>
+        <v>584580</v>
       </c>
       <c r="R13" t="n">
-        <v>7056965</v>
+        <v>7057147</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,22 +2047,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120108467</v>
+        <v>120108141</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584625</v>
+        <v>584574</v>
       </c>
       <c r="R14" t="n">
-        <v>7057173</v>
+        <v>7057137</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,22 +2164,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120107534</v>
+        <v>120107381</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,16 +2192,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2210,16 +2210,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584364</v>
+        <v>584368</v>
       </c>
       <c r="R15" t="n">
-        <v>7056956</v>
+        <v>7056918</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2256,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,12 +2266,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,22 +2281,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120108290</v>
+        <v>120107534</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584580</v>
+        <v>584364</v>
       </c>
       <c r="R16" t="n">
-        <v>7057147</v>
+        <v>7056956</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,12 +2398,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 36470-2024 artfynd.xlsx
+++ b/artfynd/A 36470-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120107871</v>
+        <v>120108290</v>
       </c>
       <c r="B2" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584459</v>
+        <v>584580</v>
       </c>
       <c r="R2" t="n">
-        <v>7056926</v>
+        <v>7057147</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120107799</v>
+        <v>120108467</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584425</v>
+        <v>584625</v>
       </c>
       <c r="R3" t="n">
-        <v>7056965</v>
+        <v>7057173</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,19 +897,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120107400</v>
+        <v>120108535</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584327</v>
+        <v>584643</v>
       </c>
       <c r="R4" t="n">
-        <v>7056918</v>
+        <v>7057141</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1133,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120108359</v>
+        <v>120107799</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1173,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584598</v>
+        <v>584425</v>
       </c>
       <c r="R6" t="n">
-        <v>7057170</v>
+        <v>7056965</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1243,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120108467</v>
+        <v>120107871</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584625</v>
+        <v>584459</v>
       </c>
       <c r="R7" t="n">
-        <v>7057173</v>
+        <v>7056926</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,12 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120108535</v>
+        <v>120108009</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584643</v>
+        <v>584477</v>
       </c>
       <c r="R8" t="n">
-        <v>7057141</v>
+        <v>7056963</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,12 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120108343</v>
+        <v>120108359</v>
       </c>
       <c r="B9" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,42 +1495,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584643</v>
+        <v>584598</v>
       </c>
       <c r="R9" t="n">
-        <v>7057141</v>
+        <v>7057170</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1564,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,22 +1584,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120108385</v>
+        <v>120107381</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,34 +1612,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584601</v>
+        <v>584368</v>
       </c>
       <c r="R10" t="n">
-        <v>7057163</v>
+        <v>7056918</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120108009</v>
+        <v>120107534</v>
       </c>
       <c r="B11" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,21 +1729,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584477</v>
+        <v>584364</v>
       </c>
       <c r="R11" t="n">
-        <v>7056963</v>
+        <v>7056956</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1798,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,22 +1818,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120107427</v>
+        <v>120107400</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,42 +1846,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584332</v>
+        <v>584327</v>
       </c>
       <c r="R12" t="n">
-        <v>7056924</v>
+        <v>7056918</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1915,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1947,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120108290</v>
+        <v>120107427</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,37 +1963,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584580</v>
+        <v>584332</v>
       </c>
       <c r="R13" t="n">
-        <v>7057147</v>
+        <v>7056924</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2017,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,12 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,22 +2052,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120108141</v>
+        <v>120108385</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2075,21 +2080,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2099,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584574</v>
+        <v>584601</v>
       </c>
       <c r="R14" t="n">
-        <v>7057137</v>
+        <v>7057163</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,12 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,22 +2164,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120107381</v>
+        <v>120108141</v>
       </c>
       <c r="B15" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,16 +2192,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2210,21 +2210,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584368</v>
+        <v>584574</v>
       </c>
       <c r="R15" t="n">
-        <v>7056918</v>
+        <v>7057137</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2266,7 +2261,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,22 +2281,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120107534</v>
+        <v>120108343</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2309,37 +2309,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584364</v>
+        <v>584643</v>
       </c>
       <c r="R16" t="n">
-        <v>7056956</v>
+        <v>7057141</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2368,7 +2373,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2378,12 +2383,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 36470-2024 artfynd.xlsx
+++ b/artfynd/A 36470-2024 artfynd.xlsx
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120107871</v>
+        <v>120108009</v>
       </c>
       <c r="B7" t="n">
-        <v>90576</v>
+        <v>82321</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584459</v>
+        <v>584477</v>
       </c>
       <c r="R7" t="n">
-        <v>7056926</v>
+        <v>7056963</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120108009</v>
+        <v>120107871</v>
       </c>
       <c r="B8" t="n">
-        <v>82321</v>
+        <v>90576</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584477</v>
+        <v>584459</v>
       </c>
       <c r="R8" t="n">
-        <v>7056963</v>
+        <v>7056926</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2064,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120108385</v>
+        <v>120108141</v>
       </c>
       <c r="B14" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,21 +2080,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584601</v>
+        <v>584574</v>
       </c>
       <c r="R14" t="n">
-        <v>7057163</v>
+        <v>7057137</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,7 +2149,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,22 +2169,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120108141</v>
+        <v>120108385</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,21 +2197,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2216,10 +2221,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584574</v>
+        <v>584601</v>
       </c>
       <c r="R15" t="n">
-        <v>7057137</v>
+        <v>7057163</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2256,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,12 +2266,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,12 +2281,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 36470-2024 artfynd.xlsx
+++ b/artfynd/A 36470-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108290</v>
+        <v>120108009</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584580</v>
+        <v>584477</v>
       </c>
       <c r="R2" t="n">
-        <v>7057147</v>
+        <v>7056963</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108467</v>
+        <v>120107799</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584625</v>
+        <v>584425</v>
       </c>
       <c r="R3" t="n">
-        <v>7057173</v>
+        <v>7056965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,19 +892,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108535</v>
+        <v>120108290</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584643</v>
+        <v>584580</v>
       </c>
       <c r="R4" t="n">
-        <v>7057141</v>
+        <v>7057147</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108230</v>
+        <v>120107400</v>
       </c>
       <c r="B5" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584514</v>
+        <v>584327</v>
       </c>
       <c r="R5" t="n">
-        <v>7057145</v>
+        <v>7056918</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,19 +1126,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120107799</v>
+        <v>120108359</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584425</v>
+        <v>584598</v>
       </c>
       <c r="R6" t="n">
-        <v>7056965</v>
+        <v>7057170</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,22 +1243,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120108009</v>
+        <v>120108535</v>
       </c>
       <c r="B7" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584477</v>
+        <v>584643</v>
       </c>
       <c r="R7" t="n">
-        <v>7056963</v>
+        <v>7057141</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1340,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,22 +1360,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120107871</v>
+        <v>120107427</v>
       </c>
       <c r="B8" t="n">
-        <v>90576</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,37 +1388,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584459</v>
+        <v>584332</v>
       </c>
       <c r="R8" t="n">
-        <v>7056926</v>
+        <v>7056924</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,19 +1477,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120108359</v>
+        <v>120107534</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1519,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584598</v>
+        <v>584364</v>
       </c>
       <c r="R9" t="n">
-        <v>7057170</v>
+        <v>7056956</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,12 +1574,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,22 +1594,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120107381</v>
+        <v>120108385</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,39 +1622,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584368</v>
+        <v>584601</v>
       </c>
       <c r="R10" t="n">
-        <v>7056918</v>
+        <v>7057163</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120107534</v>
+        <v>120108230</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,21 +1734,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1753,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584364</v>
+        <v>584514</v>
       </c>
       <c r="R11" t="n">
-        <v>7056956</v>
+        <v>7057145</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,12 +1803,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,22 +1818,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120107400</v>
+        <v>120108343</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,37 +1846,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584327</v>
+        <v>584643</v>
       </c>
       <c r="R12" t="n">
-        <v>7056918</v>
+        <v>7057141</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1905,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,12 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120107427</v>
+        <v>120107871</v>
       </c>
       <c r="B13" t="n">
-        <v>57473</v>
+        <v>90576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1963,42 +1963,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584332</v>
+        <v>584459</v>
       </c>
       <c r="R13" t="n">
-        <v>7056924</v>
+        <v>7056926</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2027,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,22 +2047,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120108141</v>
+        <v>120107381</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,16 +2075,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2098,16 +2093,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584574</v>
+        <v>584368</v>
       </c>
       <c r="R14" t="n">
-        <v>7057137</v>
+        <v>7056918</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,12 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,22 +2164,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120108385</v>
+        <v>120108141</v>
       </c>
       <c r="B15" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,21 +2192,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2221,10 +2216,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584601</v>
+        <v>584574</v>
       </c>
       <c r="R15" t="n">
-        <v>7057163</v>
+        <v>7057137</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2266,7 +2261,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,22 +2281,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120108343</v>
+        <v>120108467</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2309,42 +2309,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584643</v>
+        <v>584625</v>
       </c>
       <c r="R16" t="n">
-        <v>7057141</v>
+        <v>7057173</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2373,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,7 +2378,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,12 +2398,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 36470-2024 artfynd.xlsx
+++ b/artfynd/A 36470-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108009</v>
+        <v>120107381</v>
       </c>
       <c r="B2" t="n">
-        <v>82321</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584477</v>
+        <v>584368</v>
       </c>
       <c r="R2" t="n">
-        <v>7056963</v>
+        <v>7056918</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120107799</v>
+        <v>120107871</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584425</v>
+        <v>584459</v>
       </c>
       <c r="R3" t="n">
-        <v>7056965</v>
+        <v>7056926</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,19 +892,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108290</v>
+        <v>120107534</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584580</v>
+        <v>584364</v>
       </c>
       <c r="R4" t="n">
-        <v>7057147</v>
+        <v>7056956</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120107400</v>
+        <v>120108385</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584327</v>
+        <v>584601</v>
       </c>
       <c r="R5" t="n">
-        <v>7056918</v>
+        <v>7057163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,19 +1121,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120108359</v>
+        <v>120108290</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1178,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584598</v>
+        <v>584580</v>
       </c>
       <c r="R6" t="n">
-        <v>7057170</v>
+        <v>7057147</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1255,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120108535</v>
+        <v>120108230</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584643</v>
+        <v>584514</v>
       </c>
       <c r="R7" t="n">
-        <v>7057141</v>
+        <v>7057145</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,12 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,22 +1350,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120107427</v>
+        <v>120107400</v>
       </c>
       <c r="B8" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,42 +1378,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584332</v>
+        <v>584327</v>
       </c>
       <c r="R8" t="n">
-        <v>7056924</v>
+        <v>7056918</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120107534</v>
+        <v>120108141</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1529,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584364</v>
+        <v>584574</v>
       </c>
       <c r="R9" t="n">
-        <v>7056956</v>
+        <v>7057137</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1606,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120108385</v>
+        <v>120107427</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
+        <v>57473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,37 +1612,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584601</v>
+        <v>584332</v>
       </c>
       <c r="R10" t="n">
-        <v>7057163</v>
+        <v>7056924</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1681,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,22 +1701,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120108230</v>
+        <v>120107799</v>
       </c>
       <c r="B11" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,21 +1729,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1758,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584514</v>
+        <v>584425</v>
       </c>
       <c r="R11" t="n">
-        <v>7057145</v>
+        <v>7056965</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1798,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,22 +1818,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120108343</v>
+        <v>120108009</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>82321</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,42 +1846,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584643</v>
+        <v>584477</v>
       </c>
       <c r="R12" t="n">
-        <v>7057141</v>
+        <v>7056963</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,22 +1930,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120107871</v>
+        <v>120108535</v>
       </c>
       <c r="B13" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1963,21 +1958,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1987,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584459</v>
+        <v>584643</v>
       </c>
       <c r="R13" t="n">
-        <v>7056926</v>
+        <v>7057141</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2027,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,22 +2047,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120107381</v>
+        <v>120108359</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2075,16 +2075,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2093,21 +2093,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584368</v>
+        <v>584598</v>
       </c>
       <c r="R14" t="n">
-        <v>7056918</v>
+        <v>7057170</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,7 +2144,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,7 +2176,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120108141</v>
+        <v>120108467</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584574</v>
+        <v>584625</v>
       </c>
       <c r="R15" t="n">
-        <v>7057137</v>
+        <v>7057173</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,22 +2281,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120108467</v>
+        <v>120108343</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2309,37 +2309,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584625</v>
+        <v>584643</v>
       </c>
       <c r="R16" t="n">
-        <v>7057173</v>
+        <v>7057141</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2368,7 +2373,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2378,12 +2383,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,12 +2398,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 36470-2024 artfynd.xlsx
+++ b/artfynd/A 36470-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120107871</v>
+        <v>120108385</v>
       </c>
       <c r="B3" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584459</v>
+        <v>584601</v>
       </c>
       <c r="R3" t="n">
-        <v>7056926</v>
+        <v>7057163</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120107534</v>
+        <v>120107427</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,37 +920,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584364</v>
+        <v>584332</v>
       </c>
       <c r="R4" t="n">
-        <v>7056956</v>
+        <v>7056924</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108385</v>
+        <v>120108535</v>
       </c>
       <c r="B5" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584601</v>
+        <v>584643</v>
       </c>
       <c r="R5" t="n">
-        <v>7057163</v>
+        <v>7057141</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,19 +1126,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120108290</v>
+        <v>120107400</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1173,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584580</v>
+        <v>584327</v>
       </c>
       <c r="R6" t="n">
-        <v>7057147</v>
+        <v>7056918</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1243,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120108230</v>
+        <v>120107799</v>
       </c>
       <c r="B7" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584514</v>
+        <v>584425</v>
       </c>
       <c r="R7" t="n">
-        <v>7057145</v>
+        <v>7056965</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1340,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,19 +1360,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120107400</v>
+        <v>120108359</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1402,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584327</v>
+        <v>584598</v>
       </c>
       <c r="R8" t="n">
-        <v>7056918</v>
+        <v>7057170</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,12 +1457,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,12 +1477,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1596,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120107427</v>
+        <v>120108009</v>
       </c>
       <c r="B10" t="n">
-        <v>57473</v>
+        <v>82321</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,42 +1622,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584332</v>
+        <v>584477</v>
       </c>
       <c r="R10" t="n">
-        <v>7056924</v>
+        <v>7056963</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1676,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,19 +1706,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120107799</v>
+        <v>120107534</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1753,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584425</v>
+        <v>584364</v>
       </c>
       <c r="R11" t="n">
-        <v>7056965</v>
+        <v>7056956</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1803,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1830,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120108009</v>
+        <v>120107871</v>
       </c>
       <c r="B12" t="n">
-        <v>82321</v>
+        <v>90576</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,21 +1851,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1870,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584477</v>
+        <v>584459</v>
       </c>
       <c r="R12" t="n">
-        <v>7056963</v>
+        <v>7056926</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1947,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120108535</v>
+        <v>120108343</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,24 +1963,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
@@ -1988,7 +1998,7 @@
         <v>7057141</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2017,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,12 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,7 +2064,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120108359</v>
+        <v>120108290</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -2099,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584598</v>
+        <v>584580</v>
       </c>
       <c r="R14" t="n">
-        <v>7057170</v>
+        <v>7057147</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2176,10 +2181,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120108467</v>
+        <v>120108230</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,21 +2197,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2216,10 +2221,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584625</v>
+        <v>584514</v>
       </c>
       <c r="R15" t="n">
-        <v>7057173</v>
+        <v>7057145</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2256,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,12 +2266,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2293,10 +2293,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120108343</v>
+        <v>120108467</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2309,42 +2309,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584643</v>
+        <v>584625</v>
       </c>
       <c r="R16" t="n">
-        <v>7057141</v>
+        <v>7057173</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2373,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,7 +2378,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,12 +2398,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 36470-2024 artfynd.xlsx
+++ b/artfynd/A 36470-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120107427</v>
+        <v>120108535</v>
       </c>
       <c r="B4" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,42 +920,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584332</v>
+        <v>584643</v>
       </c>
       <c r="R4" t="n">
-        <v>7056924</v>
+        <v>7057141</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108535</v>
+        <v>120107427</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,37 +1037,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584643</v>
+        <v>584332</v>
       </c>
       <c r="R5" t="n">
-        <v>7057141</v>
+        <v>7056924</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36470-2024 artfynd.xlsx
+++ b/artfynd/A 36470-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120107381</v>
+        <v>120107427</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584368</v>
+        <v>584332</v>
       </c>
       <c r="R2" t="n">
-        <v>7056918</v>
+        <v>7056924</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108385</v>
+        <v>120107799</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584601</v>
+        <v>584425</v>
       </c>
       <c r="R3" t="n">
-        <v>7057163</v>
+        <v>7056965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108535</v>
+        <v>120107871</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584643</v>
+        <v>584459</v>
       </c>
       <c r="R4" t="n">
-        <v>7057141</v>
+        <v>7056926</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120107427</v>
+        <v>120108385</v>
       </c>
       <c r="B5" t="n">
-        <v>57473</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,42 +1037,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584332</v>
+        <v>584601</v>
       </c>
       <c r="R5" t="n">
-        <v>7056924</v>
+        <v>7057163</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120107400</v>
+        <v>120108009</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584327</v>
+        <v>584477</v>
       </c>
       <c r="R6" t="n">
-        <v>7056918</v>
+        <v>7056963</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,22 +1233,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120107799</v>
+        <v>120108230</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584425</v>
+        <v>584514</v>
       </c>
       <c r="R7" t="n">
-        <v>7056965</v>
+        <v>7057145</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,12 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,19 +1345,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120108359</v>
+        <v>120107534</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1412,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584598</v>
+        <v>584364</v>
       </c>
       <c r="R8" t="n">
-        <v>7057170</v>
+        <v>7056956</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1442,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,19 +1462,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120108141</v>
+        <v>120107400</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1529,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584574</v>
+        <v>584327</v>
       </c>
       <c r="R9" t="n">
-        <v>7057137</v>
+        <v>7056918</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,12 +1559,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120108009</v>
+        <v>120108359</v>
       </c>
       <c r="B10" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1646,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584477</v>
+        <v>584598</v>
       </c>
       <c r="R10" t="n">
-        <v>7056963</v>
+        <v>7057170</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1676,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120107534</v>
+        <v>120107381</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,16 +1724,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1752,16 +1742,21 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584364</v>
+        <v>584368</v>
       </c>
       <c r="R11" t="n">
-        <v>7056956</v>
+        <v>7056918</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,12 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,22 +1813,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120107871</v>
+        <v>120108343</v>
       </c>
       <c r="B12" t="n">
-        <v>90576</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,37 +1841,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584459</v>
+        <v>584643</v>
       </c>
       <c r="R12" t="n">
-        <v>7056926</v>
+        <v>7057141</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,22 +1930,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120108343</v>
+        <v>120108290</v>
       </c>
       <c r="B13" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1963,42 +1958,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584643</v>
+        <v>584580</v>
       </c>
       <c r="R13" t="n">
-        <v>7057141</v>
+        <v>7057147</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2027,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2027,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,19 +2047,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120108290</v>
+        <v>120108141</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -2104,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584580</v>
+        <v>584574</v>
       </c>
       <c r="R14" t="n">
-        <v>7057147</v>
+        <v>7057137</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,12 +2144,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,22 +2164,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120108230</v>
+        <v>120108535</v>
       </c>
       <c r="B15" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,21 +2192,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2221,10 +2216,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584514</v>
+        <v>584643</v>
       </c>
       <c r="R15" t="n">
-        <v>7057145</v>
+        <v>7057141</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2266,7 +2261,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,12 +2281,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 36470-2024 artfynd.xlsx
+++ b/artfynd/A 36470-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120107427</v>
+        <v>120108290</v>
       </c>
       <c r="B2" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584332</v>
+        <v>584580</v>
       </c>
       <c r="R2" t="n">
-        <v>7056924</v>
+        <v>7057147</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120107799</v>
+        <v>120108343</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +808,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584425</v>
+        <v>584643</v>
       </c>
       <c r="R3" t="n">
-        <v>7056965</v>
+        <v>7057141</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120107871</v>
+        <v>120108535</v>
       </c>
       <c r="B4" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584459</v>
+        <v>584643</v>
       </c>
       <c r="R4" t="n">
-        <v>7056926</v>
+        <v>7057141</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108385</v>
+        <v>120108467</v>
       </c>
       <c r="B5" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584601</v>
+        <v>584625</v>
       </c>
       <c r="R5" t="n">
-        <v>7057163</v>
+        <v>7057173</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120108009</v>
+        <v>120107799</v>
       </c>
       <c r="B6" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584477</v>
+        <v>584425</v>
       </c>
       <c r="R6" t="n">
-        <v>7056963</v>
+        <v>7056965</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1248,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120108230</v>
+        <v>120108359</v>
       </c>
       <c r="B7" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584514</v>
+        <v>584598</v>
       </c>
       <c r="R7" t="n">
-        <v>7057145</v>
+        <v>7057170</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120107534</v>
+        <v>120108385</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584364</v>
+        <v>584601</v>
       </c>
       <c r="R8" t="n">
-        <v>7056956</v>
+        <v>7057163</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,12 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,22 +1477,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120107400</v>
+        <v>120107381</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,16 +1505,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1508,13 +1523,18 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584327</v>
+        <v>584368</v>
       </c>
       <c r="R9" t="n">
         <v>7056918</v>
@@ -1549,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,12 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,22 +1594,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120108359</v>
+        <v>120107427</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,37 +1622,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584598</v>
+        <v>584332</v>
       </c>
       <c r="R10" t="n">
-        <v>7057170</v>
+        <v>7056924</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1666,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,12 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,22 +1711,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120107381</v>
+        <v>120107534</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,16 +1739,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1742,21 +1757,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584368</v>
+        <v>584364</v>
       </c>
       <c r="R11" t="n">
-        <v>7056918</v>
+        <v>7056956</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1808,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,22 +1828,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120108343</v>
+        <v>120108141</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,42 +1856,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584643</v>
+        <v>584574</v>
       </c>
       <c r="R12" t="n">
-        <v>7057141</v>
+        <v>7057137</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1905,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1925,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1957,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120108290</v>
+        <v>120107871</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,21 +1973,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1982,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584580</v>
+        <v>584459</v>
       </c>
       <c r="R13" t="n">
-        <v>7057147</v>
+        <v>7056926</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,12 +2042,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,10 +2069,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120108141</v>
+        <v>120108230</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2075,21 +2085,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2099,10 +2109,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584574</v>
+        <v>584514</v>
       </c>
       <c r="R14" t="n">
-        <v>7057137</v>
+        <v>7057145</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,7 +2144,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,12 +2154,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,22 +2169,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120108535</v>
+        <v>120108009</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,21 +2197,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2216,10 +2221,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584643</v>
+        <v>584477</v>
       </c>
       <c r="R15" t="n">
-        <v>7057141</v>
+        <v>7056963</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2256,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,12 +2266,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,19 +2281,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120108467</v>
+        <v>120107400</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584625</v>
+        <v>584327</v>
       </c>
       <c r="R16" t="n">
-        <v>7057173</v>
+        <v>7056918</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,12 +2398,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 36470-2024 artfynd.xlsx
+++ b/artfynd/A 36470-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108009</v>
+        <v>120107871</v>
       </c>
       <c r="B2" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584477</v>
+        <v>584459</v>
       </c>
       <c r="R2" t="n">
-        <v>7056963</v>
+        <v>7056926</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120107534</v>
+        <v>120108009</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584364</v>
+        <v>584477</v>
       </c>
       <c r="R3" t="n">
-        <v>7056956</v>
+        <v>7056963</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,27 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120107799</v>
+        <v>120108230</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584425</v>
+        <v>584514</v>
       </c>
       <c r="R4" t="n">
-        <v>7056965</v>
+        <v>7057145</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,62 +984,62 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108230</v>
+        <v>120107381</v>
       </c>
       <c r="B5" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584514</v>
+        <v>584368</v>
       </c>
       <c r="R5" t="n">
-        <v>7057145</v>
+        <v>7056918</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,15 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120108343</v>
+        <v>120107400</v>
       </c>
       <c r="B6" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,42 +1119,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584643</v>
+        <v>584327</v>
       </c>
       <c r="R6" t="n">
-        <v>7057141</v>
+        <v>7056918</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1188,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,15 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120108385</v>
+        <v>120107534</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584601</v>
+        <v>584364</v>
       </c>
       <c r="R7" t="n">
-        <v>7057163</v>
+        <v>7056956</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1300,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,27 +1320,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120107871</v>
+        <v>120107799</v>
       </c>
       <c r="B8" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1378,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584459</v>
+        <v>584425</v>
       </c>
       <c r="R8" t="n">
-        <v>7056926</v>
+        <v>7056965</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1412,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,27 +1432,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120108535</v>
+        <v>120108141</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584643</v>
+        <v>584574</v>
       </c>
       <c r="R9" t="n">
-        <v>7057141</v>
+        <v>7057137</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1591,15 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120107381</v>
+        <v>120108290</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,16 +1567,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1625,21 +1585,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584368</v>
+        <v>584580</v>
       </c>
       <c r="R10" t="n">
-        <v>7056918</v>
+        <v>7057147</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1636,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,12 +1671,7 @@
         <v>120108359</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,15 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120108290</v>
+        <v>120108467</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584580</v>
+        <v>584625</v>
       </c>
       <c r="R12" t="n">
-        <v>7057147</v>
+        <v>7057173</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1860,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1942,15 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120108141</v>
+        <v>120108535</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584574</v>
+        <v>584643</v>
       </c>
       <c r="R13" t="n">
-        <v>7057137</v>
+        <v>7057141</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +1962,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +1972,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2062,12 +2007,7 @@
         <v>120107427</v>
       </c>
       <c r="B14" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2176,15 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120107400</v>
+        <v>120108343</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,37 +2127,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hästmyran, Hästmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584327</v>
+        <v>584643</v>
       </c>
       <c r="R15" t="n">
-        <v>7056918</v>
+        <v>7057141</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2251,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,12 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,123 +2225,6 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>120108467</v>
-      </c>
-      <c r="B16" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Hästmyran, Hästmyran, Ång</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>584625</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7057173</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Ramsele</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36470-2024 artfynd.xlsx
+++ b/artfynd/A 36470-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120107871</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120108009</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120108230</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120107381</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120107400</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120107534</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120107799</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120108141</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1665,6 +1710,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120108290</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1777,6 +1827,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120108359</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1889,6 +1944,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120108467</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2001,6 +2061,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120108535</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2113,6 +2178,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120107427</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2225,8 +2295,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120108343</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>